--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484052_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484052_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7265</v>
+        <v>3.4565</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1738</v>
+        <v>4.7916</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4473</v>
+        <v>-1.3351</v>
       </c>
       <c r="G2" t="n">
         <v>2.5387</v>
@@ -610,13 +610,13 @@
         <v>1.7855</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1973</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0056</v>
+        <v>0.6122</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1917</v>
+        <v>-0.0794</v>
       </c>
       <c r="V2" t="n">
         <v>-0.4085</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. BORRERO PERLAZA</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3959</v>
+        <v>3.0214</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6795</v>
+        <v>3.3172</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7164</v>
+        <v>-0.2958</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2051</v>
+        <v>1.9562</v>
       </c>
       <c r="H3" t="n">
-        <v>0.056</v>
+        <v>4.1832</v>
       </c>
       <c r="I3" t="n">
-        <v>0.149</v>
+        <v>-2.227</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0849</v>
+        <v>3.5843</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0849</v>
+        <v>4.2244</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0.29</v>
+        <v>-1.6281</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1409</v>
+        <v>-0.0412</v>
       </c>
       <c r="O3" t="n">
-        <v>0.149</v>
+        <v>-1.587</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9758</v>
+        <v>-2.1822</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3887</v>
+        <v>2.579</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8375</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5337</v>
+        <v>0.7086</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3037</v>
+        <v>-0.6434</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9405</v>
+        <v>0.6032</v>
       </c>
       <c r="W3" t="n">
         <v>1.2065</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.907</v>
+        <v>1.7894</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4766</v>
+        <v>0.4992</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4305</v>
+        <v>1.2902</v>
       </c>
       <c r="G4" t="n">
         <v>-3.006</v>
@@ -766,13 +766,13 @@
         <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1114</v>
+        <v>1.9938</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6155</v>
+        <v>1.6382</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4959</v>
+        <v>0.3556</v>
       </c>
       <c r="V4" t="n">
         <v>1.8097</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>B. BORRERO PERLAZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7274</v>
+        <v>1.1115</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4159</v>
+        <v>-0.3804</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6885</v>
+        <v>1.492</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9562</v>
+        <v>0.2051</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1832</v>
+        <v>0.056</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.227</v>
+        <v>0.149</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5843</v>
+        <v>-0.0849</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2244</v>
+        <v>-0.0849</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6281</v>
+        <v>0.29</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0412</v>
+        <v>0.1409</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.587</v>
+        <v>0.149</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3968</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1822</v>
+        <v>-2.9758</v>
       </c>
       <c r="R5" t="n">
-        <v>2.579</v>
+        <v>1.3887</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2288</v>
+        <v>1.5531</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1926</v>
+        <v>1.4738</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0362</v>
+        <v>0.0793</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6032</v>
+        <v>0.9405</v>
       </c>
       <c r="W5" t="n">
         <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6032</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3014</v>
+        <v>0.9321</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0387</v>
+        <v>0.1463</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2627</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>-1.7017</v>
@@ -922,13 +922,13 @@
         <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.1856</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1872</v>
+        <v>0.2948</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3677</v>
+        <v>-0.1092</v>
       </c>
       <c r="V6" t="n">
         <v>0.266</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7967</v>
+        <v>0.6932</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8375</v>
+        <v>0.5938</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0408</v>
+        <v>0.0994</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1325</v>
@@ -1000,13 +1000,13 @@
         <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1276</v>
+        <v>0.0241</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3061</v>
+        <v>0.0624</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1786</v>
+        <v>-0.0383</v>
       </c>
       <c r="V7" t="n">
         <v>1.2065</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3829</v>
+        <v>-1.1905</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7312</v>
+        <v>-0.5668</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-0.6237</v>
       </c>
       <c r="G8" t="n">
         <v>-1.413</v>
@@ -1078,13 +1078,13 @@
         <v>0.1984</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1683</v>
+        <v>0.0241</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.051</v>
+        <v>0.1134</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. QUIROS LOPEZ</t>
+          <t>P. SANTIAGO PAZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5567</v>
+        <v>-1.4919</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0711</v>
+        <v>-1.6074</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6278</v>
+        <v>0.1155</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.283</v>
+        <v>-0.7522</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1314</v>
+        <v>-0.3778</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1517</v>
+        <v>-0.3745</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1087</v>
+        <v>-0.2406</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0686</v>
+        <v>0.555</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0402</v>
+        <v>-0.7956</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3918</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1999</v>
+        <v>-0.9327</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1918</v>
+        <v>0.4211</v>
       </c>
       <c r="P9" t="n">
         <v>-1.3887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>-3.1741</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5236</v>
+        <v>0.649</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3548</v>
+        <v>0.6009</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1688</v>
+        <v>0.0481</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.4085</v>
+        <v>1.2065</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. SANTIAGO PAZ</t>
+          <t>A. QUIROS LOPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2554</v>
+        <v>-2.845</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2025</v>
+        <v>-0.8245</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0528</v>
+        <v>-2.0206</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7522</v>
+        <v>-1.283</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3778</v>
+        <v>-0.1314</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3745</v>
+        <v>-1.1517</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2406</v>
+        <v>1.1087</v>
       </c>
       <c r="K10" t="n">
-        <v>0.555</v>
+        <v>1.0686</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7956</v>
+        <v>0.0402</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-2.3918</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9327</v>
+        <v>-1.1999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4211</v>
+        <v>-1.1918</v>
       </c>
       <c r="P10" t="n">
         <v>-1.3887</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1741</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7855</v>
+        <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1145</v>
+        <v>0.2352</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0057</v>
+        <v>0.4592</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1202</v>
+        <v>-0.224</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2065</v>
+        <v>-0.4085</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7969</v>
+        <v>-2.8777</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.199</v>
+        <v>-3.4201</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4021</v>
+        <v>0.5424</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6038</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8701</v>
+        <v>0.7893</v>
       </c>
       <c r="T11" t="n">
-        <v>0.873</v>
+        <v>0.6519</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0029</v>
+        <v>0.1374</v>
       </c>
       <c r="V11" t="n">
         <v>0.532</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. GAVALDA GUILLEN</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3572</v>
+        <v>-3.3148</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4353</v>
+        <v>-3.1372</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9219</v>
+        <v>-0.1775</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8871</v>
+        <v>-3.6658</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6757</v>
+        <v>-0.2014</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2113</v>
+        <v>-3.4643</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2394</v>
+        <v>-1.7114</v>
       </c>
       <c r="K12" t="n">
-        <v>0.121</v>
+        <v>0.4446</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3604</v>
+        <v>-2.156</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.9544</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7967</v>
+        <v>-0.646</v>
       </c>
       <c r="O12" t="n">
-        <v>0.149</v>
+        <v>-1.3084</v>
       </c>
       <c r="P12" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1903</v>
+        <v>-2.1822</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5871</v>
+        <v>2.579</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.454</v>
+        <v>0.0255</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0056</v>
+        <v>0.8277</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4484</v>
+        <v>-0.8022</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.4129</v>
+        <v>-0.0713</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.0713</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>J. GAVALDA GUILLEN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7528</v>
+        <v>-3.6609</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4069</v>
+        <v>-1.8232</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3459</v>
+        <v>-1.8377</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6658</v>
+        <v>-1.8871</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2014</v>
+        <v>-0.6757</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.4643</v>
+        <v>-1.2113</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.7114</v>
+        <v>-1.2394</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4446</v>
+        <v>0.121</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.156</v>
+        <v>-1.3604</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.9544</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.646</v>
+        <v>-0.7967</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3084</v>
+        <v>0.149</v>
       </c>
       <c r="P13" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1822</v>
+        <v>-1.1903</v>
       </c>
       <c r="R13" t="n">
-        <v>2.579</v>
+        <v>1.5871</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4125</v>
+        <v>0.2423</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.442</v>
+        <v>0.6066</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9705</v>
+        <v>-0.3642</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0713</v>
+        <v>-2.4129</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0713</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.246999999999997</v>
+        <v>-4.3767</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.2818</v>
+        <v>-2.411499999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.965</v>
+        <v>-1.9651</v>
       </c>
       <c r="G14" t="n">
         <v>-13.7451</v>
       </c>
       <c r="H14" t="n">
-        <v>1.639400000000002</v>
+        <v>1.639400000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-15.3844</v>
@@ -1522,7 +1522,7 @@
         <v>-0.3581000000000003</v>
       </c>
       <c r="K14" t="n">
-        <v>7.1892</v>
+        <v>7.189200000000001</v>
       </c>
       <c r="L14" t="n">
         <v>-7.5471</v>
@@ -1531,10 +1531,10 @@
         <v>-13.387</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.549600000000001</v>
+        <v>-5.5496</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.8375</v>
+        <v>-7.837499999999999</v>
       </c>
       <c r="P14" t="n">
         <v>0.9919</v>
@@ -1546,16 +1546,16 @@
         <v>18.8467</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4497</v>
+        <v>6.319999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>6.1792</v>
+        <v>8.049700000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.7297</v>
+        <v>-1.7296</v>
       </c>
       <c r="V14" t="n">
-        <v>2.056700000000001</v>
+        <v>2.0567</v>
       </c>
       <c r="W14" t="n">
         <v>7.7518</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.2328</v>
+        <v>11.2914</v>
       </c>
       <c r="E15" t="n">
-        <v>8.4031</v>
+        <v>9.321400000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8297</v>
+        <v>1.97</v>
       </c>
       <c r="G15" t="n">
         <v>7.0795</v>
@@ -1624,13 +1624,13 @@
         <v>2.9758</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5276</v>
+        <v>-0.4691</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9238</v>
+        <v>-0.0056</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6038</v>
+        <v>-0.4635</v>
       </c>
       <c r="V15" t="n">
         <v>2.8955</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4413</v>
+        <v>4.0033</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8743</v>
+        <v>3.3844</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5671</v>
+        <v>0.6189</v>
       </c>
       <c r="G16" t="n">
         <v>3.4372</v>
@@ -1702,13 +1702,13 @@
         <v>1.1903</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4902</v>
+        <v>-0.9282</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5498</v>
+        <v>-0.0396</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9404</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>1.4943</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2092</v>
+        <v>3.2934</v>
       </c>
       <c r="E17" t="n">
         <v>1.2745</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9347</v>
+        <v>2.0189</v>
       </c>
       <c r="G17" t="n">
         <v>1.668</v>
@@ -1780,13 +1780,13 @@
         <v>0.1984</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0062</v>
+        <v>0.0779</v>
       </c>
       <c r="T17" t="n">
         <v>-0.051</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0448</v>
+        <v>0.1289</v>
       </c>
       <c r="V17" t="n">
         <v>1.349</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2426</v>
+        <v>0.9961</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5757</v>
+        <v>-0.6778</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8184</v>
+        <v>1.6739</v>
       </c>
       <c r="G18" t="n">
         <v>1.0909</v>
@@ -1858,13 +1858,13 @@
         <v>2.7774</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0567</v>
+        <v>-0.3033</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5726</v>
+        <v>0.4706</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6293</v>
+        <v>-0.7739</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3866</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. VILLAR CANTERO</t>
+          <t>H. OLAGUIBE GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2844</v>
+        <v>-0.3166</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1396</v>
+        <v>-1.1484</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1448</v>
+        <v>0.8318</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1694</v>
+        <v>-2.4597</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2565</v>
+        <v>2.4513</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1996</v>
+        <v>0.3378</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6399</v>
+        <v>-1.1482</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5597</v>
+        <v>1.486</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2867</v>
+        <v>-0.3463</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5295</v>
+        <v>-1.3115</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8162</v>
+        <v>0.9653</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5952</v>
+        <v>-0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.1741</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5952</v>
+        <v>3.1741</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6366000000000001</v>
+        <v>-0.4535</v>
       </c>
       <c r="T19" t="n">
-        <v>1.06</v>
+        <v>0.2155</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4235</v>
+        <v>-0.669</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6032</v>
+        <v>0.1453</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6032</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>H. OLAGUIBE GONZALEZ</t>
+          <t>I. VILLAR CANTERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7145</v>
+        <v>-0.8345</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6585</v>
+        <v>-0.8538</v>
       </c>
       <c r="F20" t="n">
-        <v>0.944</v>
+        <v>0.0193</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4597</v>
+        <v>-1.1694</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4513</v>
+        <v>0.2565</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3378</v>
+        <v>-1.1996</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1482</v>
+        <v>-0.6399</v>
       </c>
       <c r="L20" t="n">
-        <v>1.486</v>
+        <v>-0.5597</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3463</v>
+        <v>0.2867</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3115</v>
+        <v>-0.5295</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9653</v>
+        <v>0.8162</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>0.5952</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.1741</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.1741</v>
+        <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8514</v>
+        <v>0.0864</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2946</v>
+        <v>0.3458</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5568</v>
+        <v>-0.2594</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1453</v>
+        <v>-0.6032</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3271</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CRUZ JOBACHO</t>
+          <t>L. MARTÍN LLAVERÍA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3295</v>
+        <v>-1.2361</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7903</v>
+        <v>-0.5164</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4607</v>
+        <v>-0.7197</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1515</v>
+        <v>-0.1835</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3981</v>
+        <v>1.5669</v>
       </c>
       <c r="I21" t="n">
-        <v>2.5497</v>
+        <v>-1.7504</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3158</v>
+        <v>0.056</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.009599999999999999</v>
+        <v>1.4113</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3253</v>
+        <v>-1.3553</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8358</v>
+        <v>-0.2395</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3886</v>
+        <v>0.1556</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2244</v>
+        <v>-0.3951</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
         <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6875</v>
+        <v>0.2891</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1303</v>
+        <v>0.4195</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5573</v>
+        <v>-0.1304</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2065</v>
+        <v>-1.7384</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2065</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. MARTÍN LLAVERÍA</t>
+          <t>A. CRUZ JOBACHO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4503</v>
+        <v>-1.4596</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-1.8923</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8319</v>
+        <v>0.4327</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1835</v>
+        <v>2.1515</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5669</v>
+        <v>-0.3981</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7504</v>
+        <v>2.5497</v>
       </c>
       <c r="J22" t="n">
-        <v>0.056</v>
+        <v>1.3158</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4113</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3553</v>
+        <v>1.3253</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2395</v>
+        <v>0.8358</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1556</v>
+        <v>-0.3886</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3951</v>
+        <v>1.2244</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3968</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R22" t="n">
         <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>0.07480000000000001</v>
+        <v>-0.8176</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3175</v>
+        <v>-0.2323</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2427</v>
+        <v>-0.5853</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7384</v>
+        <v>-1.2065</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.7384</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. NOGUES MARTIN</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9553</v>
+        <v>-2.5312</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6904</v>
+        <v>-1.6715</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7351</v>
+        <v>-0.8598</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.232</v>
+        <v>-0.1482</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8294</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5974</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0071</v>
+        <v>1.2305</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.972</v>
+        <v>1.1853</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0351</v>
+        <v>0.0453</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7751</v>
+        <v>-1.3788</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.2557</v>
       </c>
       <c r="O23" t="n">
-        <v>1.6325</v>
+        <v>-0.123</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9919</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.1741</v>
+        <v>-2.9758</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1822</v>
+        <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2585</v>
+        <v>-0.3911</v>
       </c>
       <c r="T23" t="n">
-        <v>1.4908</v>
+        <v>0.0738</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2323</v>
+        <v>-0.4649</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9899</v>
+        <v>-0.6032</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.9899</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>E. NOGUES MARTIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8475</v>
+        <v>-2.7834</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8755</v>
+        <v>-3.7107</v>
       </c>
       <c r="F24" t="n">
+        <v>0.9273</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.8294</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.5974</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.0071</v>
+      </c>
+      <c r="K24" t="n">
         <v>-0.972</v>
       </c>
-      <c r="G24" t="n">
-        <v>-0.1482</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-0.07049999999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-0.07779999999999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.2305</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.1853</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.0453</v>
+        <v>-0.0351</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3788</v>
+        <v>0.7751</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2557</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.123</v>
+        <v>1.6325</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3887</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9758</v>
+        <v>-3.1741</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5871</v>
+        <v>2.1822</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7074</v>
+        <v>-0.5697</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1303</v>
+        <v>0.4705</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-1.0402</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6032</v>
+        <v>-0.9899</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6032</v>
+        <v>-0.9899</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.2975</v>
+        <v>-3.4956</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2383</v>
+        <v>-1.5444</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0591</v>
+        <v>-1.9512</v>
       </c>
       <c r="G25" t="n">
         <v>-0.197</v>
@@ -2404,13 +2404,13 @@
         <v>0.3968</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0924</v>
+        <v>-0.2905</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3685</v>
+        <v>0.0624</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4609</v>
+        <v>-0.3529</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4129</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>6.246900000000002</v>
+        <v>6.927199999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>1.965200000000001</v>
+        <v>1.965</v>
       </c>
       <c r="F26" t="n">
-        <v>4.281900000000001</v>
+        <v>4.9621</v>
       </c>
       <c r="G26" t="n">
         <v>13.7451</v>
@@ -2464,7 +2464,7 @@
         <v>7.8373</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3580999999999999</v>
+        <v>0.3581</v>
       </c>
       <c r="N26" t="n">
         <v>-7.189</v>
@@ -2482,13 +2482,13 @@
         <v>17.8547</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.4495</v>
+        <v>-3.7696</v>
       </c>
       <c r="T26" t="n">
         <v>1.7296</v>
       </c>
       <c r="U26" t="n">
-        <v>-6.1793</v>
+        <v>-5.4992</v>
       </c>
       <c r="V26" t="n">
         <v>-2.0566</v>
